--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487188_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487188_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0753</v>
+        <v>10.8796</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1971</v>
+        <v>9.0549</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8782</v>
+        <v>1.8247</v>
       </c>
       <c r="G2" t="n">
         <v>11.2632</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4647</v>
+        <v>0.269</v>
       </c>
       <c r="T2" t="n">
-        <v>1.289</v>
+        <v>0.1468</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1758</v>
+        <v>0.1222</v>
       </c>
       <c r="V2" t="n">
         <v>0.6985</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1032</v>
+        <v>3.8775</v>
       </c>
       <c r="E3" t="n">
-        <v>1.757</v>
+        <v>2.3172</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3462</v>
+        <v>1.5603</v>
       </c>
       <c r="G3" t="n">
         <v>3.3684</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2882</v>
+        <v>0.4862</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3278</v>
+        <v>0.2324</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0396</v>
+        <v>0.2538</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7941</v>
+        <v>3.5744</v>
       </c>
       <c r="E4" t="n">
-        <v>0.583</v>
+        <v>1.2027</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2111</v>
+        <v>2.3717</v>
       </c>
       <c r="G4" t="n">
         <v>3.9033</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3022</v>
+        <v>-0.5219</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9227</v>
+        <v>-0.303</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3795</v>
+        <v>-0.2188</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2976</v>
+        <v>2.5514</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2508</v>
+        <v>1.451</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0468</v>
+        <v>1.1003</v>
       </c>
       <c r="G5" t="n">
         <v>2.1574</v>
@@ -844,13 +844,13 @@
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0529</v>
+        <v>0.2009</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.119</v>
+        <v>0.0813</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6895</v>
+        <v>1.982</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6866</v>
+        <v>-0.3673</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3761</v>
+        <v>2.3493</v>
       </c>
       <c r="G6" t="n">
         <v>2.6961</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4144</v>
+        <v>0.7069</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2102</v>
+        <v>0.1091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6246</v>
+        <v>0.5978</v>
       </c>
       <c r="V6" t="n">
         <v>-1.228</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0577</v>
+        <v>0.8927</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.322</v>
+        <v>0.4118</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3797</v>
+        <v>0.4809</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0699</v>
+        <v>3.6731</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.679</v>
+        <v>3.0626</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6091</v>
+        <v>0.6105</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8244</v>
+        <v>2.8784</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9058</v>
+        <v>2.7892</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>0.0893</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7544</v>
+        <v>0.7946</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2268</v>
+        <v>0.2734</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.193</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.158</v>
+        <v>-3.8602</v>
       </c>
       <c r="R7" t="n">
-        <v>0.965</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3207</v>
+        <v>0.5357</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6604</v>
+        <v>-0.1203</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3398</v>
+        <v>0.656</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4118</v>
+        <v>0.0925</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0113</v>
+        <v>1.3234</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4005</v>
+        <v>-1.2309</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6731</v>
+        <v>1.852</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0626</v>
+        <v>0.9337</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6105</v>
+        <v>0.9182</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8784</v>
+        <v>2.9862</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7892</v>
+        <v>1.6352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0893</v>
+        <v>1.3509</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7946</v>
+        <v>-1.1342</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2734</v>
+        <v>-0.7015</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5212</v>
+        <v>-0.4327</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7021</v>
+        <v>-0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8602</v>
+        <v>-2.1231</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0548</v>
+        <v>-1.0454</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5208</v>
+        <v>-0.4395</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5757</v>
+        <v>-0.6058</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.614</v>
+        <v>-0.3281</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5138</v>
+        <v>0.8999</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1278</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0692</v>
+        <v>0.0157</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2482</v>
+        <v>-1.364</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3174</v>
+        <v>1.3797</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6703</v>
+        <v>-0.0699</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4793</v>
+        <v>-0.679</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1496</v>
+        <v>0.6091</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9989</v>
+        <v>-0.8244</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2267</v>
+        <v>-0.9058</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2278</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6692</v>
+        <v>0.7544</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7474</v>
+        <v>0.2268</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9218</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0873</v>
+        <v>0.2786</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0912</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0039</v>
+        <v>-0.3398</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1941</v>
+        <v>-0.0389</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0636</v>
+        <v>-2.0885</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2577</v>
+        <v>2.0497</v>
       </c>
       <c r="G10" t="n">
-        <v>1.852</v>
+        <v>0.6703</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9337</v>
+        <v>-0.4793</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9182</v>
+        <v>1.1496</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9862</v>
+        <v>-0.9989</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6352</v>
+        <v>-1.2267</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3509</v>
+        <v>0.2278</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1342</v>
+        <v>1.6692</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7015</v>
+        <v>0.7474</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4327</v>
+        <v>0.9218</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3319</v>
+        <v>-0.1953</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6993</v>
+        <v>0.0684</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.2638</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3281</v>
+        <v>-0.8999</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2501</v>
+        <v>-0.1777</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7205</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9706</v>
+        <v>-1.158</v>
       </c>
       <c r="G11" t="n">
         <v>3.3627</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0337</v>
+        <v>0.0386</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5208</v>
+        <v>-0.2611</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4871</v>
+        <v>0.2997</v>
       </c>
       <c r="V11" t="n">
         <v>-1.842</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>23.0542</v>
+        <v>23.6492</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3265</v>
+        <v>12.9215</v>
       </c>
       <c r="F12" t="n">
         <v>10.7277</v>
@@ -1372,7 +1372,7 @@
         <v>9.635899999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>6.578799999999998</v>
+        <v>6.578799999999999</v>
       </c>
       <c r="N12" t="n">
         <v>2.734</v>
@@ -1381,7 +1381,7 @@
         <v>3.8449</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.8253</v>
+        <v>-4.825299999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.3357</v>
@@ -1390,19 +1390,19 @@
         <v>13.5105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1583999999999999</v>
+        <v>0.7532999999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4624000000000001</v>
+        <v>0.1325</v>
       </c>
       <c r="U12" t="n">
         <v>0.6209</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.1556</v>
+        <v>-5.155600000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>4.8275</v>
+        <v>4.827500000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-9.9831</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1951</v>
+        <v>1.1013</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8</v>
+        <v>0.0343</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6049</v>
+        <v>1.0669</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.4523</v>
+        <v>0.4309</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.2009</v>
+        <v>-1.3827</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.2513</v>
+        <v>1.8136</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.7001</v>
+        <v>1.5184</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.2359</v>
+        <v>-0.9885</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4641</v>
+        <v>2.5069</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.7522</v>
+        <v>-1.0875</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.965</v>
+        <v>-0.3942</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7872</v>
+        <v>-0.6933</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-2.1231</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.9301</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-1.158</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.0881</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.0756</v>
+        <v>-0.3645</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8886</v>
+        <v>-0.5889</v>
       </c>
       <c r="U13" t="n">
-        <v>0.187</v>
+        <v>0.2244</v>
       </c>
       <c r="V13" t="n">
-        <v>3.6417</v>
+        <v>1.228</v>
       </c>
       <c r="W13" t="n">
-        <v>5.7695</v>
+        <v>1.228</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DE LARREA ASENJO</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6576</v>
+        <v>0.539</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2882</v>
+        <v>2.7708</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-2.2318</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.0717</v>
+        <v>-0.3266</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4451</v>
+        <v>-0.0289</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6265</v>
+        <v>-0.2978</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0028</v>
+        <v>4.3859</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6569</v>
+        <v>3.0428</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6597</v>
+        <v>1.3431</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0689</v>
+        <v>-4.7125</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1021</v>
+        <v>-3.0717</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9668</v>
+        <v>-1.6408</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8951</v>
+        <v>-1.158</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3808</v>
+        <v>0.0357</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8725000000000001</v>
+        <v>-0.1289</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5083</v>
+        <v>0.1646</v>
       </c>
       <c r="V14" t="n">
-        <v>2.6996</v>
+        <v>-0.3281</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3135</v>
+        <v>-0.3281</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>M. DE LARREA ASENJO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3402</v>
+        <v>0.1226</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5665</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9067</v>
+        <v>-0.765</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4309</v>
+        <v>-2.0717</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3827</v>
+        <v>-0.4451</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8136</v>
+        <v>-1.6265</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5184</v>
+        <v>-0.0028</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9885</v>
+        <v>0.6569</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5069</v>
+        <v>-0.6597</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0875</v>
+        <v>-2.0689</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3942</v>
+        <v>-1.1021</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6933</v>
+        <v>-0.9668</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.193</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1231</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1257</v>
+        <v>0.8457</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1898</v>
+        <v>0.472</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0641</v>
+        <v>0.3738</v>
       </c>
       <c r="V15" t="n">
-        <v>1.228</v>
+        <v>2.6996</v>
       </c>
       <c r="W15" t="n">
-        <v>1.228</v>
+        <v>3.3135</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4587</v>
+        <v>-0.8213</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5207000000000001</v>
+        <v>2.5969</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-3.4181</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.4574</v>
+        <v>-7.4523</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4985</v>
+        <v>-5.2009</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9589</v>
+        <v>-2.2513</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.841</v>
+        <v>-2.7001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8489</v>
+        <v>-2.2359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.4641</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6164</v>
+        <v>-4.7522</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6496</v>
+        <v>-2.965</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9668</v>
+        <v>-1.7872</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3161</v>
+        <v>1.9301</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3161</v>
+        <v>3.0881</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1965</v>
+        <v>1.0593</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3617</v>
+        <v>0.6855</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8348</v>
+        <v>0.3738</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5138</v>
+        <v>3.6417</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5.7695</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5138</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.623</v>
+        <v>-1.6279</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7694</v>
+        <v>-0.3806</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3924</v>
+        <v>-1.2473</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3266</v>
+        <v>-3.4574</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0289</v>
+        <v>-2.4985</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2978</v>
+        <v>-0.9589</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3859</v>
+        <v>-0.841</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0428</v>
+        <v>-0.8489</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3431</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.7125</v>
+        <v>-2.6164</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.0717</v>
+        <v>-1.6496</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6408</v>
+        <v>-0.9668</v>
       </c>
       <c r="P17" t="n">
-        <v>1.158</v>
+        <v>2.3161</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1263</v>
+        <v>1.0272</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1303</v>
+        <v>0.4604</v>
       </c>
       <c r="U17" t="n">
-        <v>0.004</v>
+        <v>0.5668</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3281</v>
+        <v>-1.5138</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2508</v>
+        <v>-1.8635</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3921</v>
+        <v>-1.1918</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8588</v>
+        <v>-0.6717</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9005</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3503</v>
+        <v>0.037</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.119</v>
+        <v>0.0813</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2313</v>
+        <v>-0.0443</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9096</v>
+        <v>-2.6757</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.078</v>
+        <v>-1.9779</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8316</v>
+        <v>-0.6978</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7424</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5955</v>
+        <v>-0.3615</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5816</v>
+        <v>-0.4815</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0139</v>
+        <v>0.12</v>
       </c>
       <c r="V19" t="n">
         <v>0.6562</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.4101</v>
+        <v>-3.7738</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5316</v>
+        <v>-2.43</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8785</v>
+        <v>-1.3438</v>
       </c>
       <c r="G20" t="n">
         <v>-3.2171</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5441</v>
+        <v>0.0922</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0113</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="V20" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.534</v>
+        <v>-6.1195</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.7142</v>
+        <v>-4.5139</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8198</v>
+        <v>-1.6056</v>
       </c>
       <c r="G21" t="n">
         <v>-5.6351</v>
@@ -2092,13 +2092,13 @@
         <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8989</v>
+        <v>-0.4845</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7006</v>
+        <v>-0.5003</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1983</v>
+        <v>0.0159</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.0609</v>
+        <v>-6.6002</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.8235</v>
+        <v>-6.5231</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2374</v>
+        <v>-0.0771</v>
       </c>
       <c r="G22" t="n">
         <v>-5.5043</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1706</v>
+        <v>-0.7099</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0113</v>
+        <v>-0.7109</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1593</v>
+        <v>0.001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.0542</v>
+        <v>-21.719</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.7276</v>
+        <v>-10.7277</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.3265</v>
+        <v>-10.9913</v>
       </c>
       <c r="G23" t="n">
         <v>-32.8765</v>
@@ -2236,7 +2236,7 @@
         <v>-16.6618</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.6358</v>
+        <v>-9.635800000000001</v>
       </c>
       <c r="P23" t="n">
         <v>4.8251</v>
@@ -2248,16 +2248,16 @@
         <v>18.3359</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1584999999999996</v>
+        <v>1.1767</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6211000000000003</v>
+        <v>-0.621</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4626</v>
+        <v>1.798</v>
       </c>
       <c r="V23" t="n">
-        <v>5.155600000000001</v>
+        <v>5.1556</v>
       </c>
       <c r="W23" t="n">
         <v>9.982900000000001</v>
